--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>29.8041353225708</v>
+        <v>30.0500648021698</v>
       </c>
       <c r="E2" t="n">
         <v>0.9991587138518518</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>53.15427279472351</v>
+        <v>53.9701087474823</v>
       </c>
       <c r="E3" t="n">
         <v>0.9992837402469261</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>29.8041353225708</v>
+        <v>30.0500648021698</v>
       </c>
       <c r="E2" t="n">
         <v>0.9991587138518518</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>53.15427279472351</v>
+        <v>53.9701087474823</v>
       </c>
       <c r="E3" t="n">
         <v>0.9992837402469261</v>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>30.0500648021698</v>
+        <v>33.1019082069397</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9991587138518518</v>
+        <v>0.9918638859927142</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9995549535822634</v>
+        <v>0.9922241522513416</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4157303868736235</v>
+        <v>1.737732761114964</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2282322330336578</v>
+        <v>1.168828255120888</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>53.9701087474823</v>
+        <v>56.16065907478333</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9992837402469261</v>
+        <v>0.9922025775317673</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9995451828539085</v>
+        <v>0.992189257958039</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4202691667732273</v>
+        <v>1.741627454233083</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2274132467532568</v>
+        <v>1.170346040239261</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>30.0500648021698</v>
+        <v>33.1019082069397</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9991587138518518</v>
+        <v>0.9918638859927142</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9995549535822634</v>
+        <v>0.9922241522513416</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4157303868736235</v>
+        <v>1.737732761114964</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2282322330336578</v>
+        <v>1.168828255120888</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>53.9701087474823</v>
+        <v>56.16065907478333</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9992837402469261</v>
+        <v>0.9922025775317673</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9995451828539085</v>
+        <v>0.992189257958039</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4202691667732273</v>
+        <v>1.741627454233083</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2274132467532568</v>
+        <v>1.170346040239261</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>33.1019082069397</v>
+        <v>520.4395430088043</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9918638859927142</v>
+        <v>0.9444426419529058</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9922241522513416</v>
+        <v>0.949805362042893</v>
       </c>
       <c r="G2" t="n">
-        <v>1.737732761114964</v>
+        <v>39.86770444603398</v>
       </c>
       <c r="H2" t="n">
-        <v>1.168828255120888</v>
+        <v>23.62655350978136</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>56.16065907478333</v>
+        <v>973.909387588501</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9922025775317673</v>
+        <v>0.9472184077803025</v>
       </c>
       <c r="F3" t="n">
-        <v>0.992189257958039</v>
+        <v>0.9496212799586525</v>
       </c>
       <c r="G3" t="n">
-        <v>1.741627454233083</v>
+        <v>39.94074226542946</v>
       </c>
       <c r="H3" t="n">
-        <v>1.170346040239261</v>
+        <v>23.61235212888377</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10093.64454579353</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9496890772218635</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9496212799586525</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39.94074226542946</v>
+      </c>
+      <c r="H4" t="n">
+        <v>23.61235212888377</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>33.1019082069397</v>
+        <v>520.4395430088043</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9918638859927142</v>
+        <v>0.9444426419529058</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9922241522513416</v>
+        <v>0.949805362042893</v>
       </c>
       <c r="G2" t="n">
-        <v>1.737732761114964</v>
+        <v>39.86770444603398</v>
       </c>
       <c r="H2" t="n">
-        <v>1.168828255120888</v>
+        <v>23.62655350978136</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>56.16065907478333</v>
+        <v>973.909387588501</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9922025775317673</v>
+        <v>0.9472184077803025</v>
       </c>
       <c r="F3" t="n">
-        <v>0.992189257958039</v>
+        <v>0.9496212799586525</v>
       </c>
       <c r="G3" t="n">
-        <v>1.741627454233083</v>
+        <v>39.94074226542946</v>
       </c>
       <c r="H3" t="n">
-        <v>1.170346040239261</v>
+        <v>23.61235212888377</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10093.64454579353</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9496890772218635</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9496212799586525</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39.94074226542946</v>
+      </c>
+      <c r="H4" t="n">
+        <v>23.61235212888377</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>520.4395430088043</v>
+        <v>20.57877922058105</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9444426419529058</v>
+        <v>0.9918638859927142</v>
       </c>
       <c r="F2" t="n">
-        <v>0.949805362042893</v>
+        <v>0.9922241522513416</v>
       </c>
       <c r="G2" t="n">
-        <v>39.86770444603398</v>
+        <v>1.737732761114964</v>
       </c>
       <c r="H2" t="n">
-        <v>23.62655350978136</v>
+        <v>1.168828255120888</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>973.909387588501</v>
+        <v>30.65591430664062</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9472184077803025</v>
+        <v>0.9922025775317673</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9496212799586525</v>
+        <v>0.992189257958039</v>
       </c>
       <c r="G3" t="n">
-        <v>39.94074226542946</v>
+        <v>1.741627454233083</v>
       </c>
       <c r="H3" t="n">
-        <v>23.61235212888377</v>
+        <v>1.170346040239261</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10093.64454579353</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9496890772218635</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9496212799586525</v>
-      </c>
-      <c r="G4" t="n">
-        <v>39.94074226542946</v>
-      </c>
-      <c r="H4" t="n">
-        <v>23.61235212888377</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>520.4395430088043</v>
+        <v>20.57877922058105</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9444426419529058</v>
+        <v>0.9918638859927142</v>
       </c>
       <c r="F2" t="n">
-        <v>0.949805362042893</v>
+        <v>0.9922241522513416</v>
       </c>
       <c r="G2" t="n">
-        <v>39.86770444603398</v>
+        <v>1.737732761114964</v>
       </c>
       <c r="H2" t="n">
-        <v>23.62655350978136</v>
+        <v>1.168828255120888</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>973.909387588501</v>
+        <v>30.65591430664062</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9472184077803025</v>
+        <v>0.9922025775317673</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9496212799586525</v>
+        <v>0.992189257958039</v>
       </c>
       <c r="G3" t="n">
-        <v>39.94074226542946</v>
+        <v>1.741627454233083</v>
       </c>
       <c r="H3" t="n">
-        <v>23.61235212888377</v>
+        <v>1.170346040239261</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10093.64454579353</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9496890772218635</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9496212799586525</v>
-      </c>
-      <c r="G4" t="n">
-        <v>39.94074226542946</v>
-      </c>
-      <c r="H4" t="n">
-        <v>23.61235212888377</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>20.57877922058105</v>
+        <v>17.45152544975281</v>
       </c>
       <c r="E2" t="n">
         <v>0.9918638859927142</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>30.65591430664062</v>
+        <v>30.28822660446167</v>
       </c>
       <c r="E3" t="n">
         <v>0.9922025775317673</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>20.57877922058105</v>
+        <v>17.45152544975281</v>
       </c>
       <c r="E2" t="n">
         <v>0.9918638859927142</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>30.65591430664062</v>
+        <v>30.28822660446167</v>
       </c>
       <c r="E3" t="n">
         <v>0.9922025775317673</v>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>17.45152544975281</v>
+        <v>17.34539771080017</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9918638859927142</v>
+        <v>0.9917837362601486</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9922241522513416</v>
+        <v>0.9922290664125228</v>
       </c>
       <c r="G2" t="n">
-        <v>1.737732761114964</v>
+        <v>1.737183570288868</v>
       </c>
       <c r="H2" t="n">
-        <v>1.168828255120888</v>
+        <v>1.168814781769691</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>30.28822660446167</v>
+        <v>30.07380318641663</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9922025775317673</v>
+        <v>0.9921668504868879</v>
       </c>
       <c r="F3" t="n">
-        <v>0.992189257958039</v>
+        <v>0.9921835872047281</v>
       </c>
       <c r="G3" t="n">
-        <v>1.741627454233083</v>
+        <v>1.742259567523047</v>
       </c>
       <c r="H3" t="n">
-        <v>1.170346040239261</v>
+        <v>1.171631798039902</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>17.45152544975281</v>
+        <v>17.34539771080017</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9918638859927142</v>
+        <v>0.9917837362601486</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9922241522513416</v>
+        <v>0.9922290664125228</v>
       </c>
       <c r="G2" t="n">
-        <v>1.737732761114964</v>
+        <v>1.737183570288868</v>
       </c>
       <c r="H2" t="n">
-        <v>1.168828255120888</v>
+        <v>1.168814781769691</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>30.28822660446167</v>
+        <v>30.07380318641663</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9922025775317673</v>
+        <v>0.9921668504868879</v>
       </c>
       <c r="F3" t="n">
-        <v>0.992189257958039</v>
+        <v>0.9921835872047281</v>
       </c>
       <c r="G3" t="n">
-        <v>1.741627454233083</v>
+        <v>1.742259567523047</v>
       </c>
       <c r="H3" t="n">
-        <v>1.170346040239261</v>
+        <v>1.171631798039902</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>17.34539771080017</v>
+        <v>1404.211943864822</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9917837362601486</v>
+        <v>0.999964076137957</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9922290664125228</v>
+        <v>0.9999797744057466</v>
       </c>
       <c r="G2" t="n">
-        <v>1.737183570288868</v>
+        <v>0.04317378957600249</v>
       </c>
       <c r="H2" t="n">
-        <v>1.168814781769691</v>
+        <v>0.01165925849131002</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>30.07380318641663</v>
+        <v>2700.546605825424</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9921668504868879</v>
+        <v>0.9999709665251018</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9921835872047281</v>
+        <v>0.9999797744057466</v>
       </c>
       <c r="G3" t="n">
-        <v>1.742259567523047</v>
+        <v>0.04317378957600249</v>
       </c>
       <c r="H3" t="n">
-        <v>1.171631798039902</v>
+        <v>0.01165925849131002</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>17.34539771080017</v>
+        <v>1404.211943864822</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9917837362601486</v>
+        <v>0.999964076137957</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9922290664125228</v>
+        <v>0.9999797744057466</v>
       </c>
       <c r="G2" t="n">
-        <v>1.737183570288868</v>
+        <v>0.04317378957600249</v>
       </c>
       <c r="H2" t="n">
-        <v>1.168814781769691</v>
+        <v>0.01165925849131002</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>30.07380318641663</v>
+        <v>2700.546605825424</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9921668504868879</v>
+        <v>0.9999709665251018</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9921835872047281</v>
+        <v>0.9999797744057466</v>
       </c>
       <c r="G3" t="n">
-        <v>1.742259567523047</v>
+        <v>0.04317378957600249</v>
       </c>
       <c r="H3" t="n">
-        <v>1.171631798039902</v>
+        <v>0.01165925849131002</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1404.211943864822</v>
+        <v>1367.34343957901</v>
       </c>
       <c r="E2" t="n">
-        <v>0.999964076137957</v>
+        <v>0.9999644955451436</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999797744057466</v>
+        <v>0.9999797977152501</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04317378957600249</v>
+        <v>0.04314890403471399</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01165925849131002</v>
+        <v>0.01165416457877736</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2700.546605825424</v>
+        <v>3124.214328289032</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999709665251018</v>
+        <v>0.9999709602864171</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999797744057466</v>
+        <v>0.9999797506618339</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04317378957600249</v>
+        <v>0.04319912415932695</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01165925849131002</v>
+        <v>0.0117052425137929</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1404.211943864822</v>
+        <v>1367.34343957901</v>
       </c>
       <c r="E2" t="n">
-        <v>0.999964076137957</v>
+        <v>0.9999644955451436</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999797744057466</v>
+        <v>0.9999797977152501</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04317378957600249</v>
+        <v>0.04314890403471399</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01165925849131002</v>
+        <v>0.01165416457877736</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2700.546605825424</v>
+        <v>3124.214328289032</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999709665251018</v>
+        <v>0.9999709602864171</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999797744057466</v>
+        <v>0.9999797506618339</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04317378957600249</v>
+        <v>0.04319912415932695</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01165925849131002</v>
+        <v>0.0117052425137929</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1367.34343957901</v>
+        <v>110.2650170326233</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999644955451436</v>
+        <v>0.9999515226287238</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999797977152501</v>
+        <v>0.9999752515704077</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04314890403471399</v>
+        <v>0.04775769396566595</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01165416457877736</v>
+        <v>0.01317099116795414</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3124.214328289032</v>
+        <v>151.6458287239075</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999709602864171</v>
+        <v>0.9999602042730554</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999797506618339</v>
+        <v>0.9999752515704077</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04319912415932695</v>
+        <v>0.04775769396566595</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0117052425137929</v>
+        <v>0.01317099116795414</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1367.34343957901</v>
+        <v>110.2650170326233</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999644955451436</v>
+        <v>0.9999515226287238</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999797977152501</v>
+        <v>0.9999752515704077</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04314890403471399</v>
+        <v>0.04775769396566595</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01165416457877736</v>
+        <v>0.01317099116795414</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3124.214328289032</v>
+        <v>151.6458287239075</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999709602864171</v>
+        <v>0.9999602042730554</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999797506618339</v>
+        <v>0.9999752515704077</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04319912415932695</v>
+        <v>0.04775769396566595</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0117052425137929</v>
+        <v>0.01317099116795414</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>110.2650170326233</v>
+        <v>2.160319328308105</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999515226287238</v>
+        <v>0.991165133416164</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999752515704077</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04775769396566595</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01317099116795414</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>151.6458287239075</v>
+        <v>0.8476254940032959</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999602042730554</v>
+        <v>0.9915514893368013</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999752515704077</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04775769396566595</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01317099116795414</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>110.2650170326233</v>
+        <v>2.160319328308105</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999515226287238</v>
+        <v>0.991165133416164</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999752515704077</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04775769396566595</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01317099116795414</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>151.6458287239075</v>
+        <v>0.8476254940032959</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999602042730554</v>
+        <v>0.9915514893368013</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999752515704077</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04775769396566595</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01317099116795414</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.160319328308105</v>
+        <v>23.60671663284302</v>
       </c>
       <c r="E2" t="n">
-        <v>0.991165133416164</v>
+        <v>0.9401693017556561</v>
       </c>
       <c r="F2" t="n">
-        <v>0.991777204955937</v>
+        <v>0.9464218459082774</v>
       </c>
       <c r="G2" t="n">
-        <v>1.786976524979942</v>
+        <v>41.18949244604086</v>
       </c>
       <c r="H2" t="n">
-        <v>1.198261096007184</v>
+        <v>24.65244606562803</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8476254940032959</v>
+        <v>31.37227702140808</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9915514893368013</v>
+        <v>0.9427502089343068</v>
       </c>
       <c r="F3" t="n">
-        <v>0.991777204955937</v>
+        <v>0.9464218459082774</v>
       </c>
       <c r="G3" t="n">
-        <v>1.786976524979942</v>
+        <v>41.18949244604086</v>
       </c>
       <c r="H3" t="n">
-        <v>1.198261096007184</v>
+        <v>24.65244606562803</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.160319328308105</v>
+        <v>23.60671663284302</v>
       </c>
       <c r="E2" t="n">
-        <v>0.991165133416164</v>
+        <v>0.9401693017556561</v>
       </c>
       <c r="F2" t="n">
-        <v>0.991777204955937</v>
+        <v>0.9464218459082774</v>
       </c>
       <c r="G2" t="n">
-        <v>1.786976524979942</v>
+        <v>41.18949244604086</v>
       </c>
       <c r="H2" t="n">
-        <v>1.198261096007184</v>
+        <v>24.65244606562803</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8476254940032959</v>
+        <v>31.37227702140808</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9915514893368013</v>
+        <v>0.9427502089343068</v>
       </c>
       <c r="F3" t="n">
-        <v>0.991777204955937</v>
+        <v>0.9464218459082774</v>
       </c>
       <c r="G3" t="n">
-        <v>1.786976524979942</v>
+        <v>41.18949244604086</v>
       </c>
       <c r="H3" t="n">
-        <v>1.198261096007184</v>
+        <v>24.65244606562803</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>23.60671663284302</v>
+        <v>9.4547119140625</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9401693017556561</v>
+        <v>0.440544769878822</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9464218459082774</v>
+        <v>0.5134104363845593</v>
       </c>
       <c r="G2" t="n">
-        <v>41.18949244604086</v>
+        <v>0.6138815401786868</v>
       </c>
       <c r="H2" t="n">
-        <v>24.65244606562803</v>
+        <v>0.4572289270463659</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>31.37227702140808</v>
+        <v>11.32251524925232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9427502089343068</v>
+        <v>0.4659092559942006</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9464218459082774</v>
+        <v>0.5134104363845593</v>
       </c>
       <c r="G3" t="n">
-        <v>41.18949244604086</v>
+        <v>0.6138815401786868</v>
       </c>
       <c r="H3" t="n">
-        <v>24.65244606562803</v>
+        <v>0.4572289270463659</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>23.60671663284302</v>
+        <v>9.4547119140625</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9401693017556561</v>
+        <v>0.440544769878822</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9464218459082774</v>
+        <v>0.5134104363845593</v>
       </c>
       <c r="G2" t="n">
-        <v>41.18949244604086</v>
+        <v>0.6138815401786868</v>
       </c>
       <c r="H2" t="n">
-        <v>24.65244606562803</v>
+        <v>0.4572289270463659</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>31.37227702140808</v>
+        <v>11.32251524925232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9427502089343068</v>
+        <v>0.4659092559942006</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9464218459082774</v>
+        <v>0.5134104363845593</v>
       </c>
       <c r="G3" t="n">
-        <v>41.18949244604086</v>
+        <v>0.6138815401786868</v>
       </c>
       <c r="H3" t="n">
-        <v>24.65244606562803</v>
+        <v>0.4572289270463659</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>9.4547119140625</v>
+        <v>109.1507470607758</v>
       </c>
       <c r="E2" t="n">
-        <v>0.440544769878822</v>
+        <v>0.4357274358187564</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5134104363845593</v>
+        <v>0.4894214179550179</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6138815401786868</v>
+        <v>71.48011178783491</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4572289270463659</v>
+        <v>34.12331542084517</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>11.32251524925232</v>
+        <v>144.6810231208801</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4659092559942006</v>
+        <v>0.4620163922841435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5134104363845593</v>
+        <v>0.4894214179550179</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6138815401786868</v>
+        <v>71.48011178783491</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4572289270463659</v>
+        <v>34.12331542084517</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>9.4547119140625</v>
+        <v>109.1507470607758</v>
       </c>
       <c r="E2" t="n">
-        <v>0.440544769878822</v>
+        <v>0.4357274358187564</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5134104363845593</v>
+        <v>0.4894214179550179</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6138815401786868</v>
+        <v>71.48011178783491</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4572289270463659</v>
+        <v>34.12331542084517</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>11.32251524925232</v>
+        <v>144.6810231208801</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4659092559942006</v>
+        <v>0.4620163922841435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5134104363845593</v>
+        <v>0.4894214179550179</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6138815401786868</v>
+        <v>71.48011178783491</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4572289270463659</v>
+        <v>34.12331542084517</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>109.1507470607758</v>
+        <v>2.596037626266479</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4357274358187564</v>
+        <v>0.991165133416164</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4894214179550179</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G2" t="n">
-        <v>71.48011178783491</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H2" t="n">
-        <v>34.12331542084517</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>144.6810231208801</v>
+        <v>1.166927576065063</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4620163922841435</v>
+        <v>0.9915514893368013</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4894214179550179</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G3" t="n">
-        <v>71.48011178783491</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H3" t="n">
-        <v>34.12331542084517</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.238911151885986</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9918184774008527</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.991777204955937</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.786976524979942</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.198261096007184</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>109.1507470607758</v>
+        <v>2.596037626266479</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4357274358187564</v>
+        <v>0.991165133416164</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4894214179550179</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G2" t="n">
-        <v>71.48011178783491</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H2" t="n">
-        <v>34.12331542084517</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>144.6810231208801</v>
+        <v>1.166927576065063</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4620163922841435</v>
+        <v>0.9915514893368013</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4894214179550179</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G3" t="n">
-        <v>71.48011178783491</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H3" t="n">
-        <v>34.12331542084517</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.238911151885986</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9918184774008527</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.991777204955937</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.786976524979942</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.198261096007184</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.596037626266479</v>
+        <v>20.91527438163757</v>
       </c>
       <c r="E2" t="n">
-        <v>0.991165133416164</v>
+        <v>0.9401693017556561</v>
       </c>
       <c r="F2" t="n">
-        <v>0.991777204955937</v>
+        <v>0.9464218459082774</v>
       </c>
       <c r="G2" t="n">
-        <v>1.786976524979942</v>
+        <v>41.18949244604086</v>
       </c>
       <c r="H2" t="n">
-        <v>1.198261096007184</v>
+        <v>24.65244606562803</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.166927576065063</v>
+        <v>29.4542236328125</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9915514893368013</v>
+        <v>0.9427502089343068</v>
       </c>
       <c r="F3" t="n">
-        <v>0.991777204955937</v>
+        <v>0.9464218459082774</v>
       </c>
       <c r="G3" t="n">
-        <v>1.786976524979942</v>
+        <v>41.18949244604086</v>
       </c>
       <c r="H3" t="n">
-        <v>1.198261096007184</v>
+        <v>24.65244606562803</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.238911151885986</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9918184774008527</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.991777204955937</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.786976524979942</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.198261096007184</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.596037626266479</v>
+        <v>20.91527438163757</v>
       </c>
       <c r="E2" t="n">
-        <v>0.991165133416164</v>
+        <v>0.9401693017556561</v>
       </c>
       <c r="F2" t="n">
-        <v>0.991777204955937</v>
+        <v>0.9464218459082774</v>
       </c>
       <c r="G2" t="n">
-        <v>1.786976524979942</v>
+        <v>41.18949244604086</v>
       </c>
       <c r="H2" t="n">
-        <v>1.198261096007184</v>
+        <v>24.65244606562803</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.166927576065063</v>
+        <v>29.4542236328125</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9915514893368013</v>
+        <v>0.9427502089343068</v>
       </c>
       <c r="F3" t="n">
-        <v>0.991777204955937</v>
+        <v>0.9464218459082774</v>
       </c>
       <c r="G3" t="n">
-        <v>1.786976524979942</v>
+        <v>41.18949244604086</v>
       </c>
       <c r="H3" t="n">
-        <v>1.198261096007184</v>
+        <v>24.65244606562803</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.238911151885986</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9918184774008527</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.991777204955937</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.786976524979942</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.198261096007184</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>20.91527438163757</v>
+        <v>150.0820229053497</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9401693017556561</v>
+        <v>0.9999515226287238</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9464218459082774</v>
+        <v>0.9999752515704077</v>
       </c>
       <c r="G2" t="n">
-        <v>41.18949244604086</v>
+        <v>0.04775769396566595</v>
       </c>
       <c r="H2" t="n">
-        <v>24.65244606562803</v>
+        <v>0.01317099116795414</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>29.4542236328125</v>
+        <v>213.893581867218</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9427502089343068</v>
+        <v>0.9999602042730554</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9464218459082774</v>
+        <v>0.9999752515704077</v>
       </c>
       <c r="G3" t="n">
-        <v>41.18949244604086</v>
+        <v>0.04775769396566595</v>
       </c>
       <c r="H3" t="n">
-        <v>24.65244606562803</v>
+        <v>0.01317099116795414</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>20.91527438163757</v>
+        <v>150.0820229053497</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9401693017556561</v>
+        <v>0.9999515226287238</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9464218459082774</v>
+        <v>0.9999752515704077</v>
       </c>
       <c r="G2" t="n">
-        <v>41.18949244604086</v>
+        <v>0.04775769396566595</v>
       </c>
       <c r="H2" t="n">
-        <v>24.65244606562803</v>
+        <v>0.01317099116795414</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>29.4542236328125</v>
+        <v>213.893581867218</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9427502089343068</v>
+        <v>0.9999602042730554</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9464218459082774</v>
+        <v>0.9999752515704077</v>
       </c>
       <c r="G3" t="n">
-        <v>41.18949244604086</v>
+        <v>0.04775769396566595</v>
       </c>
       <c r="H3" t="n">
-        <v>24.65244606562803</v>
+        <v>0.01317099116795414</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>150.0820229053497</v>
+        <v>108.487827539444</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999515226287238</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>213.893581867218</v>
+        <v>151.3269882202148</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999602042730554</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>150.0820229053497</v>
+        <v>108.487827539444</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999515226287238</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>213.893581867218</v>
+        <v>151.3269882202148</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999602042730554</v>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>108.487827539444</v>
+        <v>111.6458830833435</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999515226287238</v>
+        <v>0.4357274358187564</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999752515704077</v>
+        <v>0.4894214179550179</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04775769396566595</v>
+        <v>71.48011178783491</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01317099116795414</v>
+        <v>34.12331542084517</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>151.3269882202148</v>
+        <v>150.6258206367493</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999602042730554</v>
+        <v>0.4620163922841435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999752515704077</v>
+        <v>0.4894214179550179</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04775769396566595</v>
+        <v>71.48011178783491</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01317099116795414</v>
+        <v>34.12331542084517</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>108.487827539444</v>
+        <v>111.6458830833435</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999515226287238</v>
+        <v>0.4357274358187564</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999752515704077</v>
+        <v>0.4894214179550179</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04775769396566595</v>
+        <v>71.48011178783491</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01317099116795414</v>
+        <v>34.12331542084517</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>151.3269882202148</v>
+        <v>150.6258206367493</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999602042730554</v>
+        <v>0.4620163922841435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999752515704077</v>
+        <v>0.4894214179550179</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04775769396566595</v>
+        <v>71.48011178783491</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01317099116795414</v>
+        <v>34.12331542084517</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>111.6458830833435</v>
+        <v>292.0688977241516</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4357274358187564</v>
+        <v>0.9102965857569525</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4894214179550179</v>
+        <v>0.9273325445472385</v>
       </c>
       <c r="G2" t="n">
-        <v>71.48011178783491</v>
+        <v>9.145823506301472</v>
       </c>
       <c r="H2" t="n">
-        <v>34.12331542084517</v>
+        <v>5.264394540992574</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>150.6258206367493</v>
+        <v>416.8807187080383</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4620163922841435</v>
+        <v>0.9158221695712907</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4894214179550179</v>
+        <v>0.9273325445472385</v>
       </c>
       <c r="G3" t="n">
-        <v>71.48011178783491</v>
+        <v>9.145823506301472</v>
       </c>
       <c r="H3" t="n">
-        <v>34.12331542084517</v>
+        <v>5.264394540992574</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>111.6458830833435</v>
+        <v>292.0688977241516</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4357274358187564</v>
+        <v>0.9102965857569525</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4894214179550179</v>
+        <v>0.9273325445472385</v>
       </c>
       <c r="G2" t="n">
-        <v>71.48011178783491</v>
+        <v>9.145823506301472</v>
       </c>
       <c r="H2" t="n">
-        <v>34.12331542084517</v>
+        <v>5.264394540992574</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>150.6258206367493</v>
+        <v>416.8807187080383</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4620163922841435</v>
+        <v>0.9158221695712907</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4894214179550179</v>
+        <v>0.9273325445472385</v>
       </c>
       <c r="G3" t="n">
-        <v>71.48011178783491</v>
+        <v>9.145823506301472</v>
       </c>
       <c r="H3" t="n">
-        <v>34.12331542084517</v>
+        <v>5.264394540992574</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>292.0688977241516</v>
+        <v>88.95418930053711</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9102965857569525</v>
+        <v>0.4632401988762054</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9273325445472385</v>
+        <v>0.5541589867760863</v>
       </c>
       <c r="G2" t="n">
-        <v>9.145823506301472</v>
+        <v>0.5876154250486469</v>
       </c>
       <c r="H2" t="n">
-        <v>5.264394540992574</v>
+        <v>0.4176122448979592</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>416.8807187080383</v>
+        <v>175.4782721996307</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9158221695712907</v>
+        <v>0.4938420438668326</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9273325445472385</v>
+        <v>0.5543425190507176</v>
       </c>
       <c r="G3" t="n">
-        <v>9.145823506301472</v>
+        <v>0.5874944654537398</v>
       </c>
       <c r="H3" t="n">
-        <v>5.264394540992574</v>
+        <v>0.4179591836734693</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>292.0688977241516</v>
+        <v>88.95418930053711</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9102965857569525</v>
+        <v>0.4632401988762054</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9273325445472385</v>
+        <v>0.5541589867760863</v>
       </c>
       <c r="G2" t="n">
-        <v>9.145823506301472</v>
+        <v>0.5876154250486469</v>
       </c>
       <c r="H2" t="n">
-        <v>5.264394540992574</v>
+        <v>0.4176122448979592</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>416.8807187080383</v>
+        <v>175.4782721996307</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9158221695712907</v>
+        <v>0.4938420438668326</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9273325445472385</v>
+        <v>0.5543425190507176</v>
       </c>
       <c r="G3" t="n">
-        <v>9.145823506301472</v>
+        <v>0.5874944654537398</v>
       </c>
       <c r="H3" t="n">
-        <v>5.264394540992574</v>
+        <v>0.4179591836734693</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>88.95418930053711</v>
+        <v>0.6931955814361572</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4632401988762054</v>
+        <v>0.991165133416164</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5541589867760863</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5876154250486469</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4176122448979592</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>175.4782721996307</v>
+        <v>1.15853476524353</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4938420438668326</v>
+        <v>0.9915514893368013</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5543425190507176</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5874944654537398</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4179591836734693</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.123363494873047</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9918184774008527</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.991777204955937</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.786976524979942</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.198261096007184</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>88.95418930053711</v>
+        <v>0.6931955814361572</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4632401988762054</v>
+        <v>0.991165133416164</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5541589867760863</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5876154250486469</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4176122448979592</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>175.4782721996307</v>
+        <v>1.15853476524353</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4938420438668326</v>
+        <v>0.9915514893368013</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5543425190507176</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5874944654537398</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4179591836734693</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.123363494873047</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9918184774008527</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.991777204955937</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.786976524979942</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.198261096007184</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6931955814361572</v>
+        <v>0.9498600959777832</v>
       </c>
       <c r="E2" t="n">
         <v>0.991165133416164</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.15853476524353</v>
+        <v>1.604457378387451</v>
       </c>
       <c r="E3" t="n">
         <v>0.9915514893368013</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.123363494873047</v>
+        <v>3.369718074798584</v>
       </c>
       <c r="E4" t="n">
         <v>0.9918184774008527</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6931955814361572</v>
+        <v>0.9498600959777832</v>
       </c>
       <c r="E2" t="n">
         <v>0.991165133416164</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.15853476524353</v>
+        <v>1.604457378387451</v>
       </c>
       <c r="E3" t="n">
         <v>0.9915514893368013</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.123363494873047</v>
+        <v>3.369718074798584</v>
       </c>
       <c r="E4" t="n">
         <v>0.9918184774008527</v>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9498600959777832</v>
+        <v>27.10186529159546</v>
       </c>
       <c r="E2" t="n">
-        <v>0.991165133416164</v>
+        <v>0.9270418266698393</v>
       </c>
       <c r="F2" t="n">
-        <v>0.991777204955937</v>
+        <v>0.924444145078114</v>
       </c>
       <c r="G2" t="n">
-        <v>1.786976524979942</v>
+        <v>36.66002480664519</v>
       </c>
       <c r="H2" t="n">
-        <v>1.198261096007184</v>
+        <v>22.35330437575353</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>1.604457378387451</v>
+        <v>57.25639843940735</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9915514893368013</v>
+        <v>0.9276906110886332</v>
       </c>
       <c r="F3" t="n">
-        <v>0.991777204955937</v>
+        <v>0.924444145078114</v>
       </c>
       <c r="G3" t="n">
-        <v>1.786976524979942</v>
+        <v>36.66002480664519</v>
       </c>
       <c r="H3" t="n">
-        <v>1.198261096007184</v>
+        <v>22.35330437575353</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3.369718074798584</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9918184774008527</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.991777204955937</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.786976524979942</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.198261096007184</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9498600959777832</v>
+        <v>27.10186529159546</v>
       </c>
       <c r="E2" t="n">
-        <v>0.991165133416164</v>
+        <v>0.9270418266698393</v>
       </c>
       <c r="F2" t="n">
-        <v>0.991777204955937</v>
+        <v>0.924444145078114</v>
       </c>
       <c r="G2" t="n">
-        <v>1.786976524979942</v>
+        <v>36.66002480664519</v>
       </c>
       <c r="H2" t="n">
-        <v>1.198261096007184</v>
+        <v>22.35330437575353</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>1.604457378387451</v>
+        <v>57.25639843940735</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9915514893368013</v>
+        <v>0.9276906110886332</v>
       </c>
       <c r="F3" t="n">
-        <v>0.991777204955937</v>
+        <v>0.924444145078114</v>
       </c>
       <c r="G3" t="n">
-        <v>1.786976524979942</v>
+        <v>36.66002480664519</v>
       </c>
       <c r="H3" t="n">
-        <v>1.198261096007184</v>
+        <v>22.35330437575353</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3.369718074798584</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9918184774008527</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.991777204955937</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.786976524979942</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.198261096007184</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>27.10186529159546</v>
+        <v>131.0292558670044</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9270418266698393</v>
+        <v>0.9999678077497777</v>
       </c>
       <c r="F2" t="n">
-        <v>0.924444145078114</v>
+        <v>0.9999805234233666</v>
       </c>
       <c r="G2" t="n">
-        <v>36.66002480664519</v>
+        <v>0.04185051084179357</v>
       </c>
       <c r="H2" t="n">
-        <v>22.35330437575353</v>
+        <v>0.01120138434431437</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>57.25639843940735</v>
+        <v>203.59889793396</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9276906110886332</v>
+        <v>0.9999725193608008</v>
       </c>
       <c r="F3" t="n">
-        <v>0.924444145078114</v>
+        <v>0.9999805234233666</v>
       </c>
       <c r="G3" t="n">
-        <v>36.66002480664519</v>
+        <v>0.04185051084179357</v>
       </c>
       <c r="H3" t="n">
-        <v>22.35330437575353</v>
+        <v>0.01120138434431437</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>27.10186529159546</v>
+        <v>131.0292558670044</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9270418266698393</v>
+        <v>0.9999678077497777</v>
       </c>
       <c r="F2" t="n">
-        <v>0.924444145078114</v>
+        <v>0.9999805234233666</v>
       </c>
       <c r="G2" t="n">
-        <v>36.66002480664519</v>
+        <v>0.04185051084179357</v>
       </c>
       <c r="H2" t="n">
-        <v>22.35330437575353</v>
+        <v>0.01120138434431437</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>57.25639843940735</v>
+        <v>203.59889793396</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9276906110886332</v>
+        <v>0.9999725193608008</v>
       </c>
       <c r="F3" t="n">
-        <v>0.924444145078114</v>
+        <v>0.9999805234233666</v>
       </c>
       <c r="G3" t="n">
-        <v>36.66002480664519</v>
+        <v>0.04185051084179357</v>
       </c>
       <c r="H3" t="n">
-        <v>22.35330437575353</v>
+        <v>0.01120138434431437</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>131.0292558670044</v>
+        <v>142.4573543071747</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999678077497777</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>203.59889793396</v>
+        <v>209.7782816886902</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999725193608008</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>131.0292558670044</v>
+        <v>142.4573543071747</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999678077497777</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>203.59889793396</v>
+        <v>209.7782816886902</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999725193608008</v>
